--- a/nr-cleaning/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="110">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:04:54+00:00</t>
+    <t>2024-03-06T15:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -256,10 +256,7 @@
 </t>
   </si>
   <si>
-    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
-  </si>
-  <si>
-    <t>Synonyme : secteurConventionnement</t>
+    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie (Synonyme : secteurConventionnement).</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -341,16 +338,13 @@
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
+    <t>Liste des conventionnements CNAM.</t>
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>required</t>
-  </si>
-  <si>
-    <t>Liste des conventionnement CNAM.</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J130-CNAMAmeliSecteurConventionnement-RASS/FHIR/JDV-J130-CNAMAmeliSecteurConventionnement-RASS</t>
@@ -694,7 +688,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="33.703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="135.0390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -857,9 +851,7 @@
       <c r="M2" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="N2" t="s" s="2">
-        <v>81</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>76</v>
@@ -917,10 +909,10 @@
         <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>76</v>
@@ -928,10 +920,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -942,25 +934,25 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1011,13 +1003,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -1026,15 +1018,15 @@
         <v>76</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1057,13 +1049,13 @@
         <v>76</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1102,19 +1094,19 @@
         <v>76</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
@@ -1123,10 +1115,10 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -1134,10 +1126,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1145,10 +1137,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
@@ -1160,16 +1152,16 @@
         <v>76</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1219,13 +1211,13 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
@@ -1234,15 +1226,15 @@
         <v>76</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1253,7 +1245,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -1265,13 +1257,13 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1298,14 +1290,12 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="Y6" s="2"/>
+      <c r="Z6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>110</v>
-      </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
       </c>
@@ -1322,22 +1312,22 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/nr-cleaning/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:16:55+00:00</t>
+    <t>2024-03-06T15:26:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-cleaning/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-ext-practitionerrole-contracted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:26:05+00:00</t>
+    <t>2024-03-06T16:31:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
